--- a/data/batches/B25_Mixed/Test_Validation_Report/Test_Validation_Report_B25.xlsx
+++ b/data/batches/B25_Mixed/Test_Validation_Report/Test_Validation_Report_B25.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,12 +746,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SD1078</t>
+          <t>SD1221</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -771,14 +771,14 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -797,37 +797,37 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Imputation mismatch</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
+          <t>Rule validation successful.</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SD1221</t>
+          <t>SD1225</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SD1225</t>
+          <t>SD1299</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TS</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SD1299</t>
+          <t>SD1452</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1065,58 +1065,58 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>66</v>
+      </c>
+      <c r="J7" t="n">
+        <v>66</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SD1452</t>
+          <t>SD2024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SD2024</t>
+          <t>SD2223</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SD2223</t>
+          <t>SD2244</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1366,26 +1366,26 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1410,110 +1410,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Missing in P21 Issue Summary</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Rule validation successful.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>B25_Mixed</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>endocrinology_t2dm</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SD2244</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Rule validation successful.</t>
+          <t>Rule ID not found in P21 Rules sheet. Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q255"/>
+  <dimension ref="A1:Q258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,10 +1627,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1737,7 +1639,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Complete Row @ CSV Row 32; count=1</t>
+          <t>Complete Row @ CSV Row 47; count=1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1747,7 +1649,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Complete Row @ CSV Row 32; count=1</t>
+          <t>Complete Row @ CSV Row 47; count=1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -22509,44 +22411,52 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SD1078</t>
+          <t>SD1299</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>INJ-SD1078-DM-001</t>
+          <t>INJ-SD1299-CM-001</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="E254" t="inlineStr"/>
       <c r="F254" t="inlineStr">
         <is>
-          <t>RFCSTDTC</t>
+          <t>EPOCH</t>
         </is>
       </c>
       <c r="G254" t="inlineStr"/>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Column not present in original</t>
+          <t>present</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>Column not present in original</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22569,7 +22479,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>New column injection verified successfully</t>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -22589,30 +22499,287 @@
           <t>CM</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr"/>
       <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>Unable to parse variables_modified</t>
+          <t>Column successfully removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SD1299</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>INJ-SD1299-CM-001</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>Column successfully removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SD1299</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>INJ-SD1299-CM-001</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>CMSTDY</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Column successfully removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SD1299</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>INJ-SD1299-CM-001</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>CMENDY</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Column successfully removed</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22729,6 +22896,104 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B25_Mixed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>endocrinology_t2dm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SD2244</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>FAIL - Missing in P21 Issue Summary</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Rule ID not found in P21 Rules sheet. Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -22861,12 +23126,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SD1078</t>
+          <t>SD2244</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22893,21 +23158,21 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -22937,12 +23202,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL - Missing in P21 Issue Summary</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Expected injection count and P21 Found count mismatch.</t>
+          <t>Rule ID not found in P21 Rules sheet. Rule ID not found in P21 Issue Summary. Expected injection count and P21 Found count mismatch.</t>
         </is>
       </c>
     </row>
@@ -22957,7 +23222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23019,6 +23284,68 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>B25_Mixed</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>endocrinology_t2dm</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SD1078</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Skipped in Error Imputation</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Rule is present in SDTM_P21 Working file for the selected batch and host generator key, but not present in Export Summary.</t>
         </is>
       </c>
     </row>
@@ -23100,16 +23427,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -23121,7 +23448,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
     </row>
   </sheetData>
